--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -109,6 +109,21 @@
   </si>
   <si>
     <t xml:space="preserve">Havana Docks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THOMAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT\&amp;T</t>
   </si>
 </sst>
 </file>
@@ -490,7 +505,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -498,7 +513,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -506,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10">
@@ -559,13 +574,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -577,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -663,10 +678,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -689,10 +704,10 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
         <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -707,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +730,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -730,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -741,25 +756,25 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="10">
@@ -767,10 +782,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -852,7 +867,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -860,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -868,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -1009,6 +1024,28 @@
         <v>30</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t xml:space="preserve">AT\&amp;T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter</t>
   </si>
 </sst>
 </file>
@@ -473,7 +479,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +487,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +503,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -505,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="8">
@@ -513,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="10">
@@ -600,7 +606,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -612,13 +618,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="4">
@@ -626,11 +632,11 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
@@ -638,13 +644,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -652,7 +658,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -667,10 +673,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>8.2</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="6">
@@ -678,13 +684,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -696,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="7">
@@ -704,10 +710,10 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -716,13 +722,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8.6</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="8">
@@ -730,7 +736,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -739,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +762,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -768,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -843,7 +849,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -851,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -859,7 +865,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -867,7 +873,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -875,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -883,7 +889,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -1046,6 +1052,17 @@
         <v>35</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -503,7 +503,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="10">
@@ -580,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -592,13 +592,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3">
@@ -684,7 +684,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -696,13 +696,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.8</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7">
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -777,10 +777,10 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +865,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -519,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="9">
@@ -580,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -592,13 +592,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="3">
@@ -736,7 +736,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -748,13 +748,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
@@ -881,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
